--- a/output/pdf_financials_xlsx/YGT.xlsx
+++ b/output/pdf_financials_xlsx/YGT.xlsx
@@ -5889,52 +5889,52 @@
         <v>0.148538</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.276507</v>
+        <v>0.284617</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.49589</v>
+        <v>0.502542</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.56692</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.610078</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.230819</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.275505</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.730592</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.213807</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.738352</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.863752</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.53703</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.342798</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.551452</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.686109</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.765142</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.84518</v>
       </c>
     </row>
     <row r="93">
@@ -6478,52 +6478,52 @@
         <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.033</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.054034</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.039034</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.0051</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.00129</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.0625</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>0.028428</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>0.006575</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.057163</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-0.009238</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-0.021214</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>0.009122999999999999</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>-0.146488</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>0.127407</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>-0.017247</v>
       </c>
       <c r="R103" s="3" t="n">
-        <v>0</v>
+        <v>0.040401</v>
       </c>
     </row>
     <row r="104">
@@ -6652,52 +6652,52 @@
         <v>0.005831</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.002038</v>
+        <v>-0.030962</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.02133</v>
+        <v>-0.075364</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.135987</v>
+        <v>-0.096953</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.06253300000000001</v>
+        <v>0.057433</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.019237</v>
+        <v>-0.020527</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.14083</v>
+        <v>-0.20333</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.07845100000000001</v>
+        <v>0.106879</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.414414</v>
+        <v>0.420989</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.338697</v>
+        <v>-0.39586</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.125602</v>
+        <v>0.116364</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.08318200000000001</v>
+        <v>-0.104396</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.027278</v>
+        <v>0.036401</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.124125</v>
+        <v>-0.022363</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.122469</v>
+        <v>0.004938</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.118689</v>
+        <v>0.101442</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>-0.07642500000000001</v>
+        <v>-0.036024</v>
       </c>
     </row>
     <row r="107">
@@ -7351,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.753961</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>-1.496872</v>
@@ -8763,7 +8763,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -9705,7 +9709,11 @@
           <t>Share-based payment reserve 9, 10</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10887,7 +10895,11 @@
           <t>Prepaids and deposits 87,290</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11814,7 +11826,11 @@
           <t>Share-based payment reserve 9, 10 4,342,798</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13729,7 +13745,11 @@
           <t>Share-based payment reserve 12, 13</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -14004,7 +14024,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -15049,7 +15073,11 @@
           <t>Share-based payment reserve 11, 12</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -16209,7 +16237,11 @@
           <t>Share-based payment reserve 10, 11</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -16308,7 +16340,11 @@
           <t>Prepaids and deposits 6</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -16712,7 +16748,11 @@
           <t>Share-based payment reserve 9, 10</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -17417,7 +17457,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -19658,7 +19702,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -23269,7 +23317,11 @@
           <t>Prepaids and deposits 9,123</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -28421,7 +28473,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -29011,7 +29067,11 @@
           <t>Increase in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/YGT.xlsx
+++ b/output/pdf_financials_xlsx/YGT.xlsx
@@ -1029,43 +1029,43 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.009258000000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001972</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006027</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.01596</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002792</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007733</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.016819</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.046546</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.078379</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.036337</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.008257</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.018388</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.021338</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1985,43 +1985,43 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.16148</v>
+        <v>-0.170738</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.063274</v>
+        <v>-1.065246</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.468434</v>
+        <v>-0.474461</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.029915</v>
+        <v>-0.045875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.384566</v>
+        <v>-1.387358</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.639552</v>
+        <v>-1.647285</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.862736</v>
+        <v>-1.879555</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.273645</v>
+        <v>-1.320191</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.15744</v>
+        <v>-1.235819</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.241148</v>
+        <v>-2.277485</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.346349</v>
+        <v>-1.354606</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.881448</v>
+        <v>-1.899836</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.325276</v>
+        <v>-2.346614</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-1.228867</v>
@@ -2101,43 +2101,43 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.16148</v>
+        <v>-0.170738</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.063274</v>
+        <v>-1.065246</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.468434</v>
+        <v>-0.474461</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.029915</v>
+        <v>-0.045875</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.384566</v>
+        <v>-1.387358</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.639552</v>
+        <v>-1.647285</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.862736</v>
+        <v>-1.879555</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.273645</v>
+        <v>-1.320191</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.15744</v>
+        <v>-1.235819</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.241148</v>
+        <v>-2.277485</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.346349</v>
+        <v>-1.354606</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.881448</v>
+        <v>-1.899836</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.325276</v>
+        <v>-2.346614</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-1.228867</v>
@@ -2450,7 +2450,7 @@
         <v>3.060107</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.095359</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>1.359296</v>
@@ -2566,7 +2566,7 @@
         <v>3.060107</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.277231</v>
+        <v>1.37259</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>1.359296</v>
@@ -3262,7 +3262,7 @@
         <v>0.257781</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.279426</v>
+        <v>0.184067</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0.178742</v>
@@ -9046,7 +9046,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -10093,7 +10097,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -11105,7 +11109,11 @@
           <t>Reclamation deposits 5 152,540</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -12737,7 +12745,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -14394,7 +14406,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -37567,7 +37583,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -40896,7 +40912,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E329" s="5" t="n">

--- a/output/pdf_financials_xlsx/YGT.xlsx
+++ b/output/pdf_financials_xlsx/YGT.xlsx
@@ -2076,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.047678</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.003973</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>-1.354606</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.899836</v>
+        <v>-1.852158</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.346614</v>
+        <v>-2.342641</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-1.228867</v>
@@ -6334,10 +6334,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.047678</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.003973</v>
       </c>
       <c r="O100" s="3" t="n">
         <v>0</v>
@@ -22612,7 +22612,11 @@
           <t>Depreciation - right-of-use assets -</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -25072,7 +25076,11 @@
           <t>Depreciation - right-of-use assets</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -36656,7 +36664,11 @@
           <t>Depreciation of right-of-use asset 4 -</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -40415,7 +40427,11 @@
           <t>Depreciation of right-of-use asset 6</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/YGT.xlsx
+++ b/output/pdf_financials_xlsx/YGT.xlsx
@@ -766,28 +766,28 @@
         <v>0.946084</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.091455</v>
+        <v>1.113955</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.59487</v>
+        <v>0.62487</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.713561</v>
+        <v>0.747061</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.749536</v>
+        <v>0.826566</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.848043</v>
+        <v>0.9200430000000001</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.770939</v>
+        <v>0.840189</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.703064</v>
+        <v>0.756064</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1.244318</v>
+        <v>1.299318</v>
       </c>
     </row>
     <row r="8">
@@ -946,22 +946,22 @@
         <v>2.011749</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.099599</v>
+        <v>1.133099</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.929226</v>
+        <v>1.006256</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.166038</v>
+        <v>1.238038</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.089415</v>
+        <v>1.158665</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.820256</v>
+        <v>0.873256</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1.438543</v>
+        <v>1.493543</v>
       </c>
     </row>
     <row r="11">
@@ -1004,22 +1004,22 @@
         <v>-2.011749</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-1.099599</v>
+        <v>-1.133099</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.929226</v>
+        <v>-1.006256</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-1.166038</v>
+        <v>-1.238038</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-1.089415</v>
+        <v>-1.158665</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.820256</v>
+        <v>-0.873256</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-1.438543</v>
+        <v>-1.493543</v>
       </c>
     </row>
     <row r="12">
@@ -1352,7 +1352,7 @@
         <v>0.202</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.195</v>
+        <v>-0.195</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.158</v>
@@ -1364,10 +1364,10 @@
         <v>0.39907</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>0.218768</v>
+        <v>-0.218768</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0.011236</v>
+        <v>0.011236</v>
       </c>
     </row>
     <row r="18">
@@ -4363,10 +4363,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0.055413</v>
@@ -6975,19 +6975,19 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003302</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004834</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004549</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="112">
@@ -7186,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.265873</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -7216,7 +7216,7 @@
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.117708</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0</v>
@@ -8355,19 +8355,19 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003302</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004834</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004549</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="135">
@@ -8413,19 +8413,19 @@
         <v>-1.778319</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-1.804916</v>
+        <v>-1.808218</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-2.182261</v>
+        <v>-2.187095</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-2.020606</v>
+        <v>-2.025155</v>
       </c>
       <c r="Q135" s="3" t="n">
         <v>-1.605944</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-2.322255</v>
+        <v>-2.325255</v>
       </c>
     </row>
   </sheetData>
@@ -18984,7 +18984,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -20046,7 +20050,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -20141,7 +20149,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -21705,7 +21717,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -22305,7 +22321,11 @@
           <t>Deferred income tax expense (recovery) 158,000</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -24876,7 +24896,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -25781,7 +25805,11 @@
           <t>Deferred income tax expenses (recovery)</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -26268,7 +26296,11 @@
           <t>Deferred income tax expenses</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -27592,7 +27624,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -30489,7 +30525,11 @@
           <t>Directors' fees 8</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -31779,7 +31819,11 @@
           <t>Deferred income tax recovery (expense) 14</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -36769,7 +36813,11 @@
           <t>Directors' fees 8 77,030</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -40530,7 +40578,11 @@
           <t>Directors' fees 11</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -41405,7 +41457,11 @@
           <t>Deferred income tax recovery 17</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -44405,7 +44461,11 @@
           <t>Directors’ fees 10</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
